--- a/file/table/TSIG_InterpolacionEspacialSimilitud.xlsx
+++ b/file/table/TSIG_InterpolacionEspacialSimilitud.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30012"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebacorreoescuelaingeduco-my.sharepoint.com/personal/william_aguilar_escuelaing_edu_co/Documents/ECIJG.ClassSourcecode/TSIG/TSIG0144/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{54683353-CBDE-405B-997F-B4CBAC7412A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{963FDBAB-8F55-4CA8-88DA-1CED1B9E388F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB9E53B-3080-42EF-8D94-8261576DACBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FADDA20A-9183-4748-AD77-0EE003FE428D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{FADDA20A-9183-4748-AD77-0EE003FE428D}"/>
   </bookViews>
   <sheets>
     <sheet name="Análisis" sheetId="1" r:id="rId1"/>
@@ -979,6 +979,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -986,7 +987,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1614,6 +1614,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1621,7 +1622,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2845,9 +2845,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2885,7 +2885,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2991,7 +2991,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3133,7 +3133,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3142,32 +3142,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D07793-14EA-4377-A050-B635B54AEB8D}">
   <dimension ref="B1:H10"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.42578125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="25.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.3984375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.3984375" style="2" customWidth="1"/>
+    <col min="5" max="6" width="25.3984375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="2.73046875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.3984375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.6">
       <c r="F1" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:8" s="4" customFormat="1" ht="33" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" s="4" customFormat="1" ht="33" x14ac:dyDescent="0.45">
       <c r="B4" s="13" t="s">
         <v>12</v>
       </c>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B6" s="16" t="s">
         <v>5</v>
       </c>
@@ -3223,7 +3223,7 @@
         <v>0.99853110361290087</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B7" s="16" t="s">
         <v>6</v>
       </c>
@@ -3242,7 +3242,7 @@
         <v>0.84896502015143982</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B8" s="16" t="s">
         <v>8</v>
       </c>
@@ -3261,7 +3261,7 @@
         <v>0.80457736218548881</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B9" s="16" t="s">
         <v>7</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>0.85359656627839497</v>
       </c>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B10" s="18" t="s">
         <v>10</v>
       </c>
@@ -3321,42 +3321,42 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFB2715-2416-4CB2-9819-9592930C09A8}">
   <dimension ref="B2:B22"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="63.85546875" style="7" customWidth="1"/>
-    <col min="3" max="16384" width="11.42578125" style="7"/>
+    <col min="1" max="1" width="2.73046875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="63.86328125" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="11.3984375" style="7"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B2" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B5" s="6"/>
     </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B7" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B22" s="10" t="s">
         <v>18</v>
       </c>
@@ -3375,12 +3375,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3593,15 +3590,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4645D1B4-DFE2-471A-8D54-4207738784F3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D102464-CD91-4CF0-9717-D53DCDB3C887}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="85273d68-90a1-4455-8abc-8dc013f26eed"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="7eeb79fa-ffdc-4bd7-a04f-d010a9c58256"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3626,18 +3635,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D102464-CD91-4CF0-9717-D53DCDB3C887}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4645D1B4-DFE2-471A-8D54-4207738784F3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="85273d68-90a1-4455-8abc-8dc013f26eed"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="7eeb79fa-ffdc-4bd7-a04f-d010a9c58256"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>